--- a/zy71220/test_subscriptions.xlsx
+++ b/zy71220/test_subscriptions.xlsx
@@ -645,28 +645,28 @@
         <v>1000000</v>
       </c>
       <c r="G2" s="2">
-        <v>46167.98667501375</v>
+        <v>46168.04255272158</v>
       </c>
       <c r="H2" s="2">
-        <v>46168.98667501375</v>
+        <v>46169.04255272158</v>
       </c>
       <c r="I2" t="s">
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>46535</v>
+        <v>46536</v>
       </c>
       <c r="K2" t="s">
         <v>46</v>
       </c>
       <c r="L2" s="3">
-        <v>46350</v>
+        <v>46351</v>
       </c>
       <c r="M2" t="s">
         <v>50</v>
       </c>
       <c r="N2" s="3">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="O2" t="s">
         <v>53</v>
@@ -707,28 +707,28 @@
         <v>500000</v>
       </c>
       <c r="G3" s="2">
-        <v>46170.48667501375</v>
+        <v>46170.54255272158</v>
       </c>
       <c r="H3" s="2">
-        <v>46170.48667501375</v>
+        <v>46170.54255272158</v>
       </c>
       <c r="I3" t="s">
         <v>42</v>
       </c>
       <c r="J3" s="3">
-        <v>46535</v>
+        <v>46536</v>
       </c>
       <c r="K3" t="s">
         <v>47</v>
       </c>
       <c r="L3" s="3">
-        <v>46350</v>
+        <v>46351</v>
       </c>
       <c r="M3" t="s">
         <v>51</v>
       </c>
       <c r="N3" s="3">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="O3" t="s">
         <v>54</v>
@@ -763,28 +763,28 @@
         <v>800000</v>
       </c>
       <c r="G4" s="2">
-        <v>46168.98667501375</v>
+        <v>46169.04255272158</v>
       </c>
       <c r="H4" s="2">
-        <v>46168.98667501375</v>
+        <v>46169.04255272158</v>
       </c>
       <c r="I4" t="s">
         <v>43</v>
       </c>
       <c r="J4" s="3">
-        <v>46535</v>
+        <v>46536</v>
       </c>
       <c r="K4" t="s">
         <v>48</v>
       </c>
       <c r="L4" s="3">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="M4" t="s">
         <v>52</v>
       </c>
       <c r="N4" s="3">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="O4" t="s">
         <v>55</v>
@@ -819,28 +819,28 @@
         <v>2000000</v>
       </c>
       <c r="G5" s="2">
-        <v>46169.98667501375</v>
+        <v>46170.04255272158</v>
       </c>
       <c r="H5" s="2">
-        <v>46169.48667501375</v>
+        <v>46169.54255272158</v>
       </c>
       <c r="I5" t="s">
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>46535</v>
+        <v>46536</v>
       </c>
       <c r="K5" t="s">
         <v>46</v>
       </c>
       <c r="L5" s="3">
-        <v>46350</v>
+        <v>46351</v>
       </c>
       <c r="M5" t="s">
         <v>50</v>
       </c>
       <c r="N5" s="3">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="O5" t="s">
         <v>56</v>
@@ -875,19 +875,19 @@
         <v>300000</v>
       </c>
       <c r="G6" s="2">
-        <v>46169.98667501375</v>
+        <v>46170.04255272158</v>
       </c>
       <c r="I6" t="s">
         <v>44</v>
       </c>
       <c r="J6" s="3">
-        <v>46535</v>
+        <v>46536</v>
       </c>
       <c r="K6" t="s">
         <v>49</v>
       </c>
       <c r="L6" s="3">
-        <v>46350</v>
+        <v>46351</v>
       </c>
       <c r="O6" t="s">
         <v>57</v>
@@ -922,16 +922,16 @@
         <v>1500000</v>
       </c>
       <c r="G7" s="2">
-        <v>46165.98667501375</v>
+        <v>46166.04255272158</v>
       </c>
       <c r="H7" s="2">
-        <v>46167.98667501375</v>
+        <v>46168.04255272158</v>
       </c>
       <c r="I7" t="s">
         <v>45</v>
       </c>
       <c r="J7" s="3">
-        <v>46535</v>
+        <v>46536</v>
       </c>
       <c r="T7" t="s">
         <v>58</v>
